--- a/etf_holdings/2026-09-14_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-14_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.80%3,800,000</t>
+          <t>11.79%3,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.79%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.54%1,380,000</t>
+          <t>9.62%1,380,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.54%</t>
+          <t>9.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.77%13,800,000</t>
+          <t>8.51%13,800,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.78%500,000</t>
+          <t>7.81%500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>7.81%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.42%5,100,000</t>
+          <t>6.45%5,100,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.91%1,000,000</t>
+          <t>5.94%1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.94%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.43%1,250,000</t>
+          <t>5.39%1,250,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.26%7,500,000</t>
+          <t>5.33%7,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.59%3,300,000</t>
+          <t>4.54%3,300,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>6669緯穎科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>-1.73%2270</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>798</v>
+        <v>2270</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.50%4,250,000</t>
+          <t>4.44%1,500,020</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4250000</v>
+        <v>1500020</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>-2.92%798</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2270</v>
+        <v>798</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.46%1,500,020</t>
+          <t>4.42%4,250,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1500020</v>
+        <v>4250000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-4.36%17885</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5620</v>
+        <v>17885</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.26%450,000</t>
+          <t>3.29%140,500</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>450000</v>
+        <v>140500</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>0%5620</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2810</v>
+        <v>5620</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.26%900,000</t>
+          <t>3.28%450,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>900000</v>
+        <v>450000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-0.71%2810</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>17885</v>
+        <v>2810</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.24%140,500</t>
+          <t>3.22%900,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>140500</v>
+        <v>900000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-09-14 23:56:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-2.15%1365</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1875</v>
+        <v>1365</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.67%1,100,000</t>
+          <t>2.76%1,500,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1100000</v>
+        <v>1500000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-0.53%1875</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1365</v>
+        <v>1875</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.64%1,500,000</t>
+          <t>2.69%1,100,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1500000</v>
+        <v>1100000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>3653健策精密</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.75%731</t>
+          <t>+0.95%5820</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>731</v>
+        <v>5820</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.59%2,700,000</t>
+          <t>2.58%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2700000</v>
+        <v>340000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3653健策精密</t>
+          <t>3026禾伸堂企</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-1.75%731</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5820</v>
+        <v>731</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.52%340,000</t>
+          <t>2.57%2,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>340000</v>
+        <v>2700000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.03%250,000</t>
+          <t>2.06%250,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.19%332.5</t>
+          <t>+0.39%510</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>332.5</v>
+        <v>510</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,34 +1846,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2317鴻海精密</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>+4.27%1955</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>248.5</v>
+        <v>1955</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.43%181</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2140</v>
+        <v>181</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,34 +1968,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.07%237</t>
+          <t>+0.52%192</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,30 +2029,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-0.53%74.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1990</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,30 +2090,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.42%142.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1955</v>
+        <v>142.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.43%181</t>
+          <t>-0.57%261.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>181</v>
+        <v>261.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,30 +2212,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2308台達電子</t>
+          <t>2357華碩電腦</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+1.08%934</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>934</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1620</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:21</t>
+          <t>2026-09-14 23:56:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5347世界先進</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-0.93%2140</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>157.5</v>
+        <v>2140</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2881富邦金融</t>
+          <t>2379瑞昱半導</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.7%154</t>
+          <t>+1.28%713</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>154</v>
+        <v>713</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,30 +2395,30 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-1.19%332.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>142.5</v>
+        <v>332.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,30 +2456,30 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.81%112.5</t>
+          <t>+1.42%142.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>112.5</v>
+        <v>142.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,30 +2517,30 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>2308台達電子</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.08%934</t>
+          <t>0%1620</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>934</v>
+        <v>1620</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2379瑞昱半導</t>
+          <t>2313華通電腦</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.28%713</t>
+          <t>-0.23%221</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>713</v>
+        <v>221</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,253</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>1253</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2885元大金融</t>
+          <t>2317鴻海精密</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.14%70.8</t>
+          <t>+0.2%248.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>70.8</v>
+        <v>248.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,360</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>9360</v>
+        <v>9000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,30 +2700,30 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2891中國信託</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.49%68.1</t>
+          <t>+1.07%237</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>68.09999999999999</v>
+        <v>237</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.39%510</t>
+          <t>+0.98%46.3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>510</v>
+        <v>46.3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>9090</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2881富邦金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.52%44.8</t>
+          <t>+3.7%154</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>44.8</v>
+        <v>154</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,30 +2883,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2882國泰金融</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.55%52.5</t>
+          <t>+1.81%112.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>52.5</v>
+        <v>112.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,30 +2944,30 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.11%46.35</t>
+          <t>+2.51%38.8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>46.35</v>
+        <v>38.8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.98%46.3</t>
+          <t>+0.11%46.35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>46.3</v>
+        <v>46.35</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2885元大金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.51%38.8</t>
+          <t>+1.14%70.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>38.8</v>
+        <v>70.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,360</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>9360</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>+1.55%52.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>261.5</v>
+        <v>52.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:22</t>
+          <t>2026-09-14 23:56:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:24</t>
+          <t>2026-09-14 23:56:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2313華通電腦</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.23%221</t>
+          <t>+2.52%44.8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>221</v>
+          <t>+2.52%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%1,253</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,7 +3278,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1253</v>
+        <v>9000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:24</t>
+          <t>2026-09-14 23:56:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,34 +3312,36 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2912統一超商</t>
+          <t>2891中國信託</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%216.5</t>
+          <t>+1.49%68.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0%9,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>216.5</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:24</t>
+          <t>2026-09-14 23:56:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3375,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2912統一超商</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.52%192</t>
+          <t>0%216.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>192</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>216.5</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:24</t>
+          <t>2026-09-14 23:56:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3438,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-3.63%1990</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.42%</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>142.5</v>
+          <t>-3.63%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:24</t>
+          <t>2026-09-14 23:56:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3501,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>5347世界先進</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.53%74.6</t>
+          <t>-2.48%157.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>74.59999999999999</v>
+          <t>-2.48%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>157.5</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,7 +3530,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
